--- a/UTCUTS/A1_Outputs/A-O_AR_Model_Base_Year.xlsx
+++ b/UTCUTS/A1_Outputs/A-O_AR_Model_Base_Year.xlsx
@@ -8199,7 +8199,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8480023E-891C-4303-A3EB-D691FADB4EF5}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{96FE837E-D42D-48E6-B5BA-2E98AE59252F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
